--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Sprint3_Backlog.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Sprint3_Backlog.xlsx
@@ -18,10 +18,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Instructivo!$A$1:$D$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sprint Backlog'!$A$1:$BR$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sprint Backlog'!$A$1:$BR$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sprint Backlog'!$1:$5,'Sprint Backlog'!$B:$F</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="110">
   <si>
     <t>SITRAFO — Lista de tareas de la iteración: Sprint 3 (propuesta para el Sprint Planning)</t>
   </si>
@@ -368,6 +368,18 @@
   </si>
   <si>
     <t>Registra la suma de todas las horas consumidas en el Sprint y las horas que restan finalmente. Las horas restantes deberían ser de cero si se logro ejecutar la tarea en su totalidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En curso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por hacer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En curso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hecho</t>
   </si>
 </sst>
 </file>
@@ -2707,10 +2719,10 @@
         <v>66</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="G15" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="7">
         <v>0</v>
@@ -2753,7 +2765,7 @@
       </c>
       <c r="V15" s="8"/>
       <c r="W15" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="7">
         <f t="shared" si="5"/>
@@ -2875,13 +2887,13 @@
         <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="G16" s="6">
         <v>2</v>
       </c>
       <c r="H16" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="7">
         <f t="shared" si="0"/>
@@ -3761,7 +3773,7 @@
       </c>
       <c r="V21" s="8"/>
       <c r="W21" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X21" s="7">
         <f t="shared" si="5"/>
@@ -3883,10 +3895,10 @@
         <v>62</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="G22" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H22" s="7">
         <v>0</v>
@@ -3929,7 +3941,7 @@
       </c>
       <c r="V22" s="8"/>
       <c r="W22" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X22" s="7">
         <f t="shared" si="5"/>
@@ -4216,195 +4228,152 @@
       <c r="F24" s="13"/>
       <c r="G24" s="13">
         <f>SUM(G6:G23)</f>
-        <v>105</v>
       </c>
       <c r="H24" s="14">
         <f>SUM(H6:H23)</f>
-        <v>10</v>
       </c>
       <c r="I24" s="14">
         <f>SUM(I6:I23)</f>
-        <v>95</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="14">
         <f>SUM(K6:K23)</f>
-        <v>2</v>
       </c>
       <c r="L24" s="14">
         <f>SUM(L6:L23)</f>
-        <v>93</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="14">
         <f>SUM(N6:N23)</f>
-        <v>14</v>
       </c>
       <c r="O24" s="14">
         <f>SUM(O6:O23)</f>
-        <v>79</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="14">
         <f>SUM(Q6:Q23)</f>
-        <v>15</v>
       </c>
       <c r="R24" s="14">
         <f>SUM(R6:R23)</f>
-        <v>64</v>
       </c>
       <c r="S24" s="15"/>
       <c r="T24" s="14">
         <f>SUM(T6:T23)</f>
-        <v>0</v>
       </c>
       <c r="U24" s="14">
         <f>SUM(U6:U23)</f>
-        <v>64</v>
       </c>
       <c r="V24" s="15"/>
       <c r="W24" s="14">
         <f>SUM(W6:W23)</f>
-        <v>0</v>
       </c>
       <c r="X24" s="14">
         <f>SUM(X6:X23)</f>
-        <v>64</v>
       </c>
       <c r="Y24" s="15"/>
       <c r="Z24" s="14">
         <f>SUM(Z6:Z23)</f>
-        <v>0</v>
       </c>
       <c r="AA24" s="14">
         <f>SUM(AA6:AA23)</f>
-        <v>64</v>
       </c>
       <c r="AB24" s="15"/>
       <c r="AC24" s="14">
         <f>SUM(AC6:AC23)</f>
-        <v>0</v>
       </c>
       <c r="AD24" s="14">
         <f>SUM(AD6:AD23)</f>
-        <v>64</v>
       </c>
       <c r="AE24" s="15"/>
       <c r="AF24" s="14">
         <f>SUM(AF6:AF23)</f>
-        <v>0</v>
       </c>
       <c r="AG24" s="14">
         <f>SUM(AG6:AG23)</f>
-        <v>64</v>
       </c>
       <c r="AH24" s="15"/>
       <c r="AI24" s="14">
         <f>SUM(AI6:AI23)</f>
-        <v>0</v>
       </c>
       <c r="AJ24" s="14">
         <f>SUM(AJ6:AJ23)</f>
-        <v>64</v>
       </c>
       <c r="AK24" s="15"/>
       <c r="AL24" s="14">
         <f>SUM(AL6:AL23)</f>
-        <v>0</v>
       </c>
       <c r="AM24" s="14">
         <f>SUM(AM6:AM23)</f>
-        <v>64</v>
       </c>
       <c r="AN24" s="15"/>
       <c r="AO24" s="14">
         <f>SUM(AO6:AO23)</f>
-        <v>0</v>
       </c>
       <c r="AP24" s="14">
         <f>SUM(AP6:AP23)</f>
-        <v>64</v>
       </c>
       <c r="AQ24" s="15"/>
       <c r="AR24" s="14">
         <f>SUM(AR6:AR23)</f>
-        <v>0</v>
       </c>
       <c r="AS24" s="14">
         <f>SUM(AS6:AS23)</f>
-        <v>64</v>
       </c>
       <c r="AT24" s="15"/>
       <c r="AU24" s="14">
         <f>SUM(AU6:AU23)</f>
-        <v>0</v>
       </c>
       <c r="AV24" s="14">
         <f>SUM(AV6:AV23)</f>
-        <v>64</v>
       </c>
       <c r="AW24" s="15"/>
       <c r="AX24" s="14">
         <f>SUM(AX6:AX23)</f>
-        <v>0</v>
       </c>
       <c r="AY24" s="14">
         <f>SUM(AY6:AY23)</f>
-        <v>64</v>
       </c>
       <c r="AZ24" s="15"/>
       <c r="BA24" s="14">
         <f>SUM(BA6:BA23)</f>
-        <v>0</v>
       </c>
       <c r="BB24" s="14">
         <f>SUM(BB6:BB23)</f>
-        <v>64</v>
       </c>
       <c r="BC24" s="15"/>
       <c r="BD24" s="14">
         <f>SUM(BD6:BD23)</f>
-        <v>0</v>
       </c>
       <c r="BE24" s="14">
         <f>SUM(BE6:BE23)</f>
-        <v>64</v>
       </c>
       <c r="BF24" s="15"/>
       <c r="BG24" s="14">
         <f>SUM(BG6:BG23)</f>
-        <v>0</v>
       </c>
       <c r="BH24" s="14">
         <f>SUM(BH6:BH23)</f>
-        <v>64</v>
       </c>
       <c r="BI24" s="15"/>
       <c r="BJ24" s="14">
         <f>SUM(BJ6:BJ23)</f>
-        <v>0</v>
       </c>
       <c r="BK24" s="14">
         <f>SUM(BK6:BK23)</f>
-        <v>64</v>
       </c>
       <c r="BL24" s="15"/>
       <c r="BM24" s="14">
         <f>SUM(BM6:BM23)</f>
-        <v>0</v>
       </c>
       <c r="BN24" s="14">
         <f>SUM(BN6:BN23)</f>
-        <v>64</v>
       </c>
       <c r="BO24" s="15"/>
       <c r="BP24" s="16">
         <f>SUM(BP6:BP23)</f>
-        <v>41</v>
       </c>
       <c r="BQ24" s="16">
         <f>SUM(BQ6:BQ23)</f>
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4476,7 +4445,6 @@
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="str">
         <f>'Sprint Backlog'!B5</f>
-        <v>Identificador (ID) de item de product backlog</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>95</v>
@@ -4485,7 +4453,6 @@
     <row r="6" spans="2:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="str">
         <f>'Sprint Backlog'!C5</f>
-        <v>Enunciado del item de Product Backlog</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>96</v>
